--- a/excel/penguins_size.xlsx
+++ b/excel/penguins_size.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14280" windowHeight="7620" firstSheet="1" activeTab="4"/>
+    <workbookView windowWidth="20490" windowHeight="7620" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="penguins_size_OG" sheetId="1" r:id="rId1"/>
@@ -154,10 +154,17 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -627,16 +634,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -645,120 +649,129 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1446,6 +1459,7 @@
             <c:dLbl>
               <c:idx val="0"/>
               <c:layout/>
+              <c:numFmt formatCode="General" sourceLinked="1"/>
               <c:spPr>
                 <a:noFill/>
                 <a:ln>
@@ -1483,6 +1497,7 @@
             <c:dLbl>
               <c:idx val="1"/>
               <c:layout/>
+              <c:numFmt formatCode="General" sourceLinked="1"/>
               <c:spPr>
                 <a:noFill/>
                 <a:ln>
@@ -1520,6 +1535,7 @@
             <c:dLbl>
               <c:idx val="2"/>
               <c:layout/>
+              <c:numFmt formatCode="General" sourceLinked="1"/>
               <c:spPr>
                 <a:noFill/>
                 <a:ln>
@@ -20980,37 +20996,37 @@
         <v>Small</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
+    <row r="5" s="1" customFormat="1" spans="1:10">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H5" t="e">
+      <c r="H5" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="I5" t="str" cm="1">
+      <c r="I5" s="2" t="str" cm="1">
         <f t="array" ref="I5">_xlfn.IFS(G5="MALE","Male",G5="FEMALE","Female",G5="NA","Unknown")</f>
         <v>Unknown</v>
       </c>
-      <c r="J5" t="e" cm="1">
+      <c r="J5" s="1" t="e" cm="1">
         <f t="array" ref="J5">_xlfn.IFS(H5&gt;=3.5,"Big",H5&lt;3.5,"Small")</f>
         <v>#VALUE!</v>
       </c>
@@ -32133,7 +32149,7 @@
         <v>9</v>
       </c>
       <c r="H323">
-        <f>F323/1000</f>
+        <f t="shared" ref="H323:H345" si="5">F323/1000</f>
         <v>5.6</v>
       </c>
       <c r="I323" t="str" cm="1">
@@ -32168,7 +32184,7 @@
         <v>10</v>
       </c>
       <c r="H324">
-        <f>F324/1000</f>
+        <f t="shared" si="5"/>
         <v>4.975</v>
       </c>
       <c r="I324" t="str" cm="1">
@@ -32203,7 +32219,7 @@
         <v>9</v>
       </c>
       <c r="H325">
-        <f>F325/1000</f>
+        <f t="shared" si="5"/>
         <v>5.5</v>
       </c>
       <c r="I325" t="str" cm="1">
@@ -32238,7 +32254,7 @@
         <v>11</v>
       </c>
       <c r="H326">
-        <f>F326/1000</f>
+        <f t="shared" si="5"/>
         <v>4.725</v>
       </c>
       <c r="I326" t="str" cm="1">
@@ -32273,7 +32289,7 @@
         <v>9</v>
       </c>
       <c r="H327">
-        <f>F327/1000</f>
+        <f t="shared" si="5"/>
         <v>5.5</v>
       </c>
       <c r="I327" t="str" cm="1">
@@ -32308,7 +32324,7 @@
         <v>10</v>
       </c>
       <c r="H328">
-        <f>F328/1000</f>
+        <f t="shared" si="5"/>
         <v>4.7</v>
       </c>
       <c r="I328" t="str" cm="1">
@@ -32343,7 +32359,7 @@
         <v>9</v>
       </c>
       <c r="H329">
-        <f>F329/1000</f>
+        <f t="shared" si="5"/>
         <v>5.5</v>
       </c>
       <c r="I329" t="str" cm="1">
@@ -32378,7 +32394,7 @@
         <v>10</v>
       </c>
       <c r="H330">
-        <f>F330/1000</f>
+        <f t="shared" si="5"/>
         <v>4.575</v>
       </c>
       <c r="I330" t="str" cm="1">
@@ -32413,7 +32429,7 @@
         <v>9</v>
       </c>
       <c r="H331">
-        <f>F331/1000</f>
+        <f t="shared" si="5"/>
         <v>5.5</v>
       </c>
       <c r="I331" t="str" cm="1">
@@ -32448,7 +32464,7 @@
         <v>10</v>
       </c>
       <c r="H332">
-        <f>F332/1000</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="I332" t="str" cm="1">
@@ -32483,7 +32499,7 @@
         <v>9</v>
       </c>
       <c r="H333">
-        <f>F333/1000</f>
+        <f t="shared" si="5"/>
         <v>5.95</v>
       </c>
       <c r="I333" t="str" cm="1">
@@ -32518,7 +32534,7 @@
         <v>10</v>
       </c>
       <c r="H334">
-        <f>F334/1000</f>
+        <f t="shared" si="5"/>
         <v>4.65</v>
       </c>
       <c r="I334" t="str" cm="1">
@@ -32553,7 +32569,7 @@
         <v>9</v>
       </c>
       <c r="H335">
-        <f>F335/1000</f>
+        <f t="shared" si="5"/>
         <v>5.5</v>
       </c>
       <c r="I335" t="str" cm="1">
@@ -32588,7 +32604,7 @@
         <v>10</v>
       </c>
       <c r="H336">
-        <f>F336/1000</f>
+        <f t="shared" si="5"/>
         <v>4.375</v>
       </c>
       <c r="I336" t="str" cm="1">
@@ -32623,7 +32639,7 @@
         <v>9</v>
       </c>
       <c r="H337">
-        <f>F337/1000</f>
+        <f t="shared" si="5"/>
         <v>5.85</v>
       </c>
       <c r="I337" t="str" cm="1">
@@ -32658,12 +32674,12 @@
         <v>16</v>
       </c>
       <c r="H338">
-        <f>F338/1000</f>
+        <f t="shared" si="5"/>
         <v>4.875</v>
       </c>
-      <c r="I338" t="e" cm="1">
-        <f t="array" ref="I338">_xlfn.IFS(G338="MALE","Male",G338="FEMALE","Female",G338="NA","Unknown")</f>
-        <v>#N/A</v>
+      <c r="I338" t="str" cm="1">
+        <f t="array" ref="I338">_xlfn.IFS(G338="MALE","Male",G338="FEMALE","Female",G338="NA","Unknown",G338=".","Unknown")</f>
+        <v>Unknown</v>
       </c>
       <c r="J338" t="str" cm="1">
         <f t="array" ref="J338">_xlfn.IFS(H338&gt;=3.5,"Big",H338&lt;3.5,"Small")</f>
@@ -32693,7 +32709,7 @@
         <v>9</v>
       </c>
       <c r="H339">
-        <f>F339/1000</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="I339" t="str" cm="1">
@@ -32728,7 +32744,7 @@
         <v>10</v>
       </c>
       <c r="H340">
-        <f>F340/1000</f>
+        <f t="shared" si="5"/>
         <v>4.925</v>
       </c>
       <c r="I340" t="str" cm="1">
@@ -32740,37 +32756,37 @@
         <v>Big</v>
       </c>
     </row>
-    <row r="341" spans="1:10">
-      <c r="A341" t="s">
+    <row r="341" s="1" customFormat="1" spans="1:10">
+      <c r="A341" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B341" t="s">
+      <c r="B341" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C341" t="s">
+      <c r="C341" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D341" t="s">
+      <c r="D341" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E341" t="s">
+      <c r="E341" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F341" t="s">
+      <c r="F341" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G341" t="s">
+      <c r="G341" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H341" t="e">
-        <f>F341/1000</f>
+      <c r="H341" s="1" t="e">
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
-      <c r="I341" t="str" cm="1">
+      <c r="I341" s="2" t="str" cm="1">
         <f t="array" ref="I341">_xlfn.IFS(G341="MALE","Male",G341="FEMALE","Female",G341="NA","Unknown")</f>
         <v>Unknown</v>
       </c>
-      <c r="J341" t="e" cm="1">
+      <c r="J341" s="1" t="e" cm="1">
         <f t="array" ref="J341">_xlfn.IFS(H341&gt;=3.5,"Big",H341&lt;3.5,"Small")</f>
         <v>#VALUE!</v>
       </c>
@@ -32798,7 +32814,7 @@
         <v>10</v>
       </c>
       <c r="H342">
-        <f>F342/1000</f>
+        <f t="shared" si="5"/>
         <v>4.85</v>
       </c>
       <c r="I342" t="str" cm="1">
@@ -32833,7 +32849,7 @@
         <v>9</v>
       </c>
       <c r="H343">
-        <f>F343/1000</f>
+        <f t="shared" si="5"/>
         <v>5.75</v>
       </c>
       <c r="I343" t="str" cm="1">
@@ -32868,7 +32884,7 @@
         <v>10</v>
       </c>
       <c r="H344">
-        <f>F344/1000</f>
+        <f t="shared" si="5"/>
         <v>5.2</v>
       </c>
       <c r="I344" t="str" cm="1">
@@ -32903,7 +32919,7 @@
         <v>9</v>
       </c>
       <c r="H345">
-        <f>F345/1000</f>
+        <f t="shared" si="5"/>
         <v>5.4</v>
       </c>
       <c r="I345" t="str" cm="1">
@@ -34107,7 +34123,6 @@
       <c r="G27">
         <v>185.6</v>
       </c>
-      <c r="H27"/>
       <c r="I27">
         <v>189.953642384106</v>
       </c>
@@ -34122,8 +34137,6 @@
       <c r="F28">
         <v>191.735294117647</v>
       </c>
-      <c r="G28"/>
-      <c r="H28"/>
       <c r="I28">
         <v>195.823529411765</v>
       </c>
@@ -34200,8 +34213,6 @@
       <c r="E35">
         <v>191.196078431373</v>
       </c>
-      <c r="F35"/>
-      <c r="G35"/>
       <c r="H35">
         <v>191.196078431373</v>
       </c>
@@ -34213,7 +34224,6 @@
       <c r="E36">
         <v>188.795454545455</v>
       </c>
-      <c r="F36"/>
       <c r="G36">
         <v>217.186991869919</v>
       </c>
@@ -34231,7 +34241,6 @@
       <c r="F37">
         <v>195.823529411765</v>
       </c>
-      <c r="G37"/>
       <c r="H37">
         <v>193.072580645161</v>
       </c>
